--- a/output/2026年4月/党费收缴子表/2026年4月-中共新疆大学计算机科学与技术学院本科生第八支部委员会-党费收缴子表.xlsx
+++ b/output/2026年4月/党费收缴子表/2026年4月-中共新疆大学计算机科学与技术学院本科生第八支部委员会-党费收缴子表.xlsx
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1147</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
@@ -620,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>1147</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="5">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>1148</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0</v>
+        <v>1148</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>1149</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
@@ -718,10 +718,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
+        <v>1149</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="7">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
@@ -767,10 +767,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="8">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
@@ -816,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1151</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="9">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="10">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>1153</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>0</v>
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0</v>
+        <v>1153</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="11">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0</v>
+        <v>1154</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0</v>
+        <v>1154</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="12">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="13">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>1156</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0</v>
+        <v>1156</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="14">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>0</v>
@@ -1110,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="15">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>1158</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0</v>
+        <v>1158</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="16">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0</v>
+        <v>1159</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0</v>
+        <v>1159</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="17">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>0</v>
@@ -1257,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="18">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0</v>
+        <v>1161</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0</v>
@@ -1306,10 +1306,10 @@
         <v>0</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0</v>
+        <v>1161</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="19">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0</v>
+        <v>1162</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>1162</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="20">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>0</v>
@@ -1404,10 +1404,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="21">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0</v>
+        <v>1164</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>1164</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="22">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0</v>
+        <v>1165</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>0</v>
@@ -1502,10 +1502,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0</v>
+        <v>1165</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="23">
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0</v>
+        <v>1166</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0</v>
+        <v>1166</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="24">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>0</v>
@@ -1600,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="25">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="26">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0</v>
+        <v>1169</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>0</v>
@@ -1698,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0</v>
+        <v>1169</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="27">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="28">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>0</v>
@@ -1796,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="29">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0</v>
+        <v>1172</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>0</v>
@@ -1845,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0</v>
+        <v>1172</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="30">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0</v>
+        <v>1173</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0</v>
+        <v>1173</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="31">
@@ -1920,15 +1920,15 @@
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>156.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A31:N31"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:N2"/>
-    <mergeCell ref="A31:N31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
